--- a/Group-List.xlsx
+++ b/Group-List.xlsx
@@ -831,7 +831,7 @@
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t>Saurabh Yadav, Shashank Singh, Ankit Kumar, Ayush Khuntiya, Ashutosh Kumar Anand</t>
+          <t>Saurabh Yadav, Shashank Singh, Ankit Kumar, Ashutosh Kumar Anand</t>
         </is>
       </c>
       <c r="C13" s="2" t="inlineStr">
